--- a/KURIKULUM2026_REVISI/011_IMPLEMENTASI_OBE_SISTEKIN2026_TABLES.xlsx
+++ b/KURIKULUM2026_REVISI/011_IMPLEMENTASI_OBE_SISTEKIN2026_TABLES.xlsx
@@ -751,14 +751,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>SISTEKIN 2026 — Sheet 9: Template Evaluasi OBE - STI-624 (Integrasi AI)</t>
+          <t>SISTEKIN 2026 — Sheet 9: Template Evaluasi OBE - STI-726 (Integrasi AI)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>TEMPLATE EVALUASI OBE - STI-624 Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>TEMPLATE EVALUASI OBE - STI-726 Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>STI-413 Machine Learning, STI-624 Integrasi AI, STI-520 Data Mining, FST-714 Skripsi</t>
+          <t>STI-413 Machine Learning, STI-726 Integrasi AI, STI-520 Data Mining, FST-714 Skripsi</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>STI-521 IoT, STI-625 Smart City, STI-519 Keamanan Lanjut, FST-714 Skripsi</t>
+          <t>STI-521 IoT, STI-727 Smart City, STI-519 Keamanan Lanjut, FST-714 Skripsi</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>STI-522 Mobile, STI-627 Platform Eng, FST-714 Skripsi</t>
+          <t>STI-522 Mobile, STI-727 Platform Eng, FST-714 Skripsi</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>STI-626 Deep Learning, STI-624 Integrasi AI, FST-610 Capstone</t>
+          <t>STI-726 Deep Learning, STI-726 Integrasi AI, FST-610 Capstone</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>STI-626 Deep Learning, STI-520 Data Mining, STA-701 MLOps</t>
+          <t>STI-726 Deep Learning, STI-520 Data Mining, STA-701 MLOps</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>STI-521 IoT, STI-625 Smart City, STB-601 Cloud DevOps, FST-714 Skripsi</t>
+          <t>STI-521 IoT, STI-727 Smart City, STB-601 Cloud DevOps, FST-714 Skripsi</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>STI-308 UI/UX, STI-522 Mobile, STI-627 Platform Eng, STC-501 UXR, FST-610 Capstone</t>
+          <t>STI-308 UI/UX, STI-522 Mobile, STI-727 Platform Eng, STC-501 UXR, FST-610 Capstone</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>STI-418 (Dasar Keamanan Informasi) = 2 SKS Teori (Sem 4). STI-625 (Smart City &amp; Pemerintahan Digital) = 2 SKS Teori Non-Praktikum (Sem 7). FST-613 (Pra-Skripsi) = 2 SKS Seminar (Sem 6).</t>
+          <t>STI-418 (Dasar Keamanan Informasi) = 2 SKS Teori (Sem 4). STI-727 (Smart City &amp; Pemerintahan Digital) = 2 SKS Teori Non-Praktikum (Sem 7). FST-613 (Pra-Skripsi) = 2 SKS Seminar (Sem 6).</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>STI-626 Deep Learning (3) / STI-627 Digital Platform Eng (3) / FST-611 Metopel (2) / FST-610 Capstone (3) / FST-612 PKL (3) / FST-613 Pra-Skripsi (2) / MK Pilihan 2 (3)</t>
+          <t>STI-726 Deep Learning (3) / STI-727 Digital Platform Eng (3) / FST-611 Metopel (2) / FST-610 Capstone (3) / FST-612 PKL (3) / FST-613 Pra-Skripsi (2) / MK Pilihan 2 (3)</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>STI-728 Startup Digital (3) / STI-624 Integrasi AI (3) / STI-625 Smart City (2) / MK Pilihan 3 (3) / MK Pilihan 4 (3) / MK Pilihan 5 (3) / MK Pilihan 6 (3)</t>
+          <t>STI-728 Startup Digital (3) / STI-726 Integrasi AI (3) / STI-727 Smart City (2) / MK Pilihan 3 (3) / MK Pilihan 4 (3) / MK Pilihan 5 (3) / MK Pilihan 6 (3)</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
@@ -11394,7 +11394,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
@@ -11443,7 +11443,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -11492,7 +11492,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
@@ -11541,7 +11541,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
@@ -12324,7 +12324,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -12376,7 +12376,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -12428,7 +12428,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -12480,7 +12480,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -13104,7 +13104,7 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -13156,7 +13156,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>STI-624: 100% OK</t>
+          <t>STI-726: 100% OK</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>STI-627: 100% OK</t>
+          <t>STI-727: 100% OK</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
